--- a/data/trans_orig/P1403-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1403-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipertensión en 2007</t>
+          <t>Población con diagnóstico de hipertensión en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>243081</t>
+          <t>241782</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>295850</t>
+          <t>298172</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>408357</t>
+          <t>406679</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>481495</t>
+          <t>474778</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>668536</t>
+          <t>665939</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>752725</t>
+          <t>758843</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,33%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>735873</t>
+          <t>733551</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>788642</t>
+          <t>789941</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>833618</t>
+          <t>840335</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>906756</t>
+          <t>908434</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1594110</t>
+          <t>1587992</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1678299</t>
+          <t>1680896</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,62%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94673</t>
+          <t>100583</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>139584</t>
+          <t>140115</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85600</t>
+          <t>84449</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>125269</t>
+          <t>122716</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>193794</t>
+          <t>194334</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>251622</t>
+          <t>251748</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1553829</t>
+          <t>1553298</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1598740</t>
+          <t>1592830</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1462404</t>
+          <t>1464957</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1502073</t>
+          <t>1503224</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3029464</t>
+          <t>3029338</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3087292</t>
+          <t>3086752</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,08%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27354</t>
+          <t>27730</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53084</t>
+          <t>52935</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18564</t>
+          <t>18747</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39531</t>
+          <t>39231</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52561</t>
+          <t>51423</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85344</t>
+          <t>84433</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>498324</t>
+          <t>498473</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>524054</t>
+          <t>523678</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>436881</t>
+          <t>437181</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>457848</t>
+          <t>457665</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>942476</t>
+          <t>943387</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>975259</t>
+          <t>976397</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,0%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>388336</t>
+          <t>391893</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>465680</t>
+          <t>469366</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>528587</t>
+          <t>533039</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>619019</t>
+          <t>616523</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>945675</t>
+          <t>948521</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1060345</t>
+          <t>1059189</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2810863</t>
+          <t>2807177</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2888207</t>
+          <t>2884650</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2760178</t>
+          <t>2762674</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2850610</t>
+          <t>2846158</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5595396</t>
+          <t>5596552</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5710066</t>
+          <t>5707220</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,75%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipertensión en 2012</t>
+          <t>Población con diagnóstico de hipertensión en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>313872</t>
+          <t>311092</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>377011</t>
+          <t>373327</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>530814</t>
+          <t>529598</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>604157</t>
+          <t>606119</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>859829</t>
+          <t>862635</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>956309</t>
+          <t>963336</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,68%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>597632</t>
+          <t>601316</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>660771</t>
+          <t>663551</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>732531</t>
+          <t>730569</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>805874</t>
+          <t>807090</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1355022</t>
+          <t>1347995</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1451502</t>
+          <t>1448696</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,68%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>162502</t>
+          <t>163790</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>216352</t>
+          <t>217640</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>123341</t>
+          <t>121670</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>172343</t>
+          <t>170806</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>302046</t>
+          <t>300721</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>373323</t>
+          <t>369702</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1747605</t>
+          <t>1746317</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1801455</t>
+          <t>1800167</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1582249</t>
+          <t>1583786</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1631251</t>
+          <t>1632922</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3345226</t>
+          <t>3348847</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3416503</t>
+          <t>3417828</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,91%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30426</t>
+          <t>30435</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58802</t>
+          <t>57745</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19609</t>
+          <t>20880</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44228</t>
+          <t>45317</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55544</t>
+          <t>58725</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93084</t>
+          <t>97761</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>422379</t>
+          <t>423436</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>450755</t>
+          <t>450746</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>414403</t>
+          <t>413314</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>439022</t>
+          <t>437751</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>846729</t>
+          <t>842052</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>884269</t>
+          <t>881088</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,75%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>534110</t>
+          <t>529237</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>624354</t>
+          <t>621894</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>696236</t>
+          <t>691301</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>794661</t>
+          <t>793759</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1251929</t>
+          <t>1256112</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1385615</t>
+          <t>1383366</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,85%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2795428</t>
+          <t>2797888</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2885672</t>
+          <t>2890545</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2755250</t>
+          <t>2756152</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2853675</t>
+          <t>2858610</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5584078</t>
+          <t>5586327</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5717764</t>
+          <t>5713581</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>81,98%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipertensión en 2016</t>
+          <t>Población con diagnóstico de hipertensión en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>205344</t>
+          <t>207551</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>252708</t>
+          <t>256707</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>346561</t>
+          <t>346715</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>410822</t>
+          <t>411020</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>568876</t>
+          <t>566218</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>646716</t>
+          <t>650027</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>37,17%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>501639</t>
+          <t>497640</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>549003</t>
+          <t>546796</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>583838</t>
+          <t>583640</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>648099</t>
+          <t>647945</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1102291</t>
+          <t>1098980</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1180131</t>
+          <t>1182789</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,63%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>202205</t>
+          <t>199305</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>258277</t>
+          <t>257339</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>190049</t>
+          <t>188429</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>249314</t>
+          <t>248610</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>402895</t>
+          <t>402763</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>487767</t>
+          <t>484674</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1818108</t>
+          <t>1819046</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1874180</t>
+          <t>1877080</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1738986</t>
+          <t>1739690</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1798251</t>
+          <t>1799871</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3576918</t>
+          <t>3580011</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3661790</t>
+          <t>3661922</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43508</t>
+          <t>42779</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72573</t>
+          <t>72631</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20372</t>
+          <t>20974</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46837</t>
+          <t>45575</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69615</t>
+          <t>69871</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109423</t>
+          <t>110774</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>474313</t>
+          <t>474255</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>503378</t>
+          <t>504107</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>502303</t>
+          <t>503565</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>528768</t>
+          <t>528166</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>986604</t>
+          <t>985253</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1026412</t>
+          <t>1026156</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>472789</t>
+          <t>474778</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>557258</t>
+          <t>562110</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>580689</t>
+          <t>578552</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>677377</t>
+          <t>676329</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1074257</t>
+          <t>1076526</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1200545</t>
+          <t>1200325</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2820360</t>
+          <t>2815508</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2904829</t>
+          <t>2902840</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2854723</t>
+          <t>2855771</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2951411</t>
+          <t>2953548</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5709173</t>
+          <t>5709393</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5835461</t>
+          <t>5833192</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,42%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipertensión en 2023</t>
+          <t>Población con diagnóstico de hipertensión en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>166597</t>
+          <t>166119</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>204852</t>
+          <t>204251</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>354916</t>
+          <t>353369</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>400597</t>
+          <t>395832</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>531923</t>
+          <t>531866</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>590618</t>
+          <t>591756</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,76%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>308541</t>
+          <t>309142</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>346796</t>
+          <t>347274</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>351450</t>
+          <t>356215</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>397131</t>
+          <t>398678</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>674822</t>
+          <t>673684</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>733517</t>
+          <t>733574</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>227634</t>
+          <t>233827</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>379021</t>
+          <t>377269</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>283776</t>
+          <t>279689</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>958306</t>
+          <t>928864</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>595871</t>
+          <t>587517</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1423387</t>
+          <t>1407601</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,12%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1909779</t>
+          <t>1911531</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2061166</t>
+          <t>2054973</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,17 +6028,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1765680</t>
+          <t>1765681</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1276559</t>
+          <t>1306002</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1951089</t>
+          <t>1955177</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3100279</t>
+          <t>3116065</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3927795</t>
+          <t>3936149</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>87,01%</t>
         </is>
       </c>
     </row>
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2234865</t>
+          <t>2234866</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2234865</t>
+          <t>2234866</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2234865</t>
+          <t>2234866</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94019</t>
+          <t>94027</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>129850</t>
+          <t>130073</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62438</t>
+          <t>63230</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86935</t>
+          <t>87847</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>163697</t>
+          <t>162333</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>205979</t>
+          <t>204839</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>515594</t>
+          <t>515371</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>551425</t>
+          <t>551417</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>573368</t>
+          <t>572456</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>597865</t>
+          <t>597073</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1099768</t>
+          <t>1100908</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1142050</t>
+          <t>1143414</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,57%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>480263</t>
+          <t>483570</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>684848</t>
+          <t>684182</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>738537</t>
+          <t>739539</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1436840</t>
+          <t>1473218</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1333545</t>
+          <t>1311747</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2083906</t>
+          <t>2095643</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,54%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2762789</t>
+          <t>2763455</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2967374</t>
+          <t>2964067</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2210376</t>
+          <t>2173998</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2908679</t>
+          <t>2907677</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5010947</t>
+          <t>4999210</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5761308</t>
+          <t>5783106</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,51%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1403-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1403-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>241782</t>
+          <t>241450</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>298172</t>
+          <t>298561</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>406679</t>
+          <t>407253</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>474778</t>
+          <t>475912</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>665939</t>
+          <t>669288</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>758843</t>
+          <t>759263</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,35%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>733551</t>
+          <t>733162</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>789941</t>
+          <t>790273</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>840335</t>
+          <t>839201</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>908434</t>
+          <t>907860</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1587992</t>
+          <t>1587572</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1680896</t>
+          <t>1677547</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>71,48%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>100583</t>
+          <t>98416</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>140115</t>
+          <t>140111</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>84449</t>
+          <t>85271</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>122716</t>
+          <t>124826</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>194334</t>
+          <t>193916</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>251748</t>
+          <t>251162</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1553298</t>
+          <t>1553302</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1592830</t>
+          <t>1594997</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1464957</t>
+          <t>1462847</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1503224</t>
+          <t>1502402</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3029338</t>
+          <t>3029924</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3086752</t>
+          <t>3087170</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,09%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27730</t>
+          <t>28398</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52935</t>
+          <t>54019</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18747</t>
+          <t>19008</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39231</t>
+          <t>39762</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51423</t>
+          <t>52494</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84433</t>
+          <t>83944</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>498473</t>
+          <t>497389</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>523678</t>
+          <t>523010</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>437181</t>
+          <t>436650</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>457665</t>
+          <t>457404</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>943387</t>
+          <t>943876</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>976397</t>
+          <t>975326</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,89%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>391893</t>
+          <t>390835</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>469366</t>
+          <t>467759</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>533039</t>
+          <t>533685</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>616523</t>
+          <t>618416</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>948521</t>
+          <t>934256</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1059189</t>
+          <t>1053357</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2807177</t>
+          <t>2808784</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2884650</t>
+          <t>2885708</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2762674</t>
+          <t>2760781</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2846158</t>
+          <t>2845512</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5596552</t>
+          <t>5602384</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5707220</t>
+          <t>5721485</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,96%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>311092</t>
+          <t>312069</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>373327</t>
+          <t>371636</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>529598</t>
+          <t>524615</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>606119</t>
+          <t>604742</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>862635</t>
+          <t>860281</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>963336</t>
+          <t>957454</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,42%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>601316</t>
+          <t>603007</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>663551</t>
+          <t>662574</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>730569</t>
+          <t>731946</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>807090</t>
+          <t>812073</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1347995</t>
+          <t>1353877</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1448696</t>
+          <t>1451050</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,78%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>163790</t>
+          <t>166241</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>217640</t>
+          <t>219860</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>121670</t>
+          <t>122666</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>170806</t>
+          <t>170538</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>300721</t>
+          <t>300088</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>369702</t>
+          <t>372405</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1746317</t>
+          <t>1744097</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1800167</t>
+          <t>1797716</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1583786</t>
+          <t>1584054</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1632922</t>
+          <t>1631926</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3348847</t>
+          <t>3346144</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3417828</t>
+          <t>3418461</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,93%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30435</t>
+          <t>31526</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57745</t>
+          <t>58971</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20880</t>
+          <t>20821</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45317</t>
+          <t>45128</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58725</t>
+          <t>56737</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97761</t>
+          <t>94682</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>423436</t>
+          <t>422210</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>450746</t>
+          <t>449655</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>413314</t>
+          <t>413503</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>437751</t>
+          <t>437810</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>842052</t>
+          <t>845131</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>881088</t>
+          <t>883076</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,96%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>529237</t>
+          <t>529119</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>621894</t>
+          <t>626223</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>691301</t>
+          <t>700216</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>793759</t>
+          <t>798613</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1256112</t>
+          <t>1256861</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1383366</t>
+          <t>1389016</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2797888</t>
+          <t>2793559</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2890545</t>
+          <t>2890663</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2756152</t>
+          <t>2751298</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2858610</t>
+          <t>2849695</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5586327</t>
+          <t>5580677</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5713581</t>
+          <t>5712832</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>81,97%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>207551</t>
+          <t>205692</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>256707</t>
+          <t>255055</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>346715</t>
+          <t>349592</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>411020</t>
+          <t>413020</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>566218</t>
+          <t>569789</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>650027</t>
+          <t>651389</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,24%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>497640</t>
+          <t>499292</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>546796</t>
+          <t>548655</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>583640</t>
+          <t>581640</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>647945</t>
+          <t>645068</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1098980</t>
+          <t>1097618</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1182789</t>
+          <t>1179218</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>67,42%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>199305</t>
+          <t>197003</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>257339</t>
+          <t>257104</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>188429</t>
+          <t>188869</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>248610</t>
+          <t>248706</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>402763</t>
+          <t>398369</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>484674</t>
+          <t>484628</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1819046</t>
+          <t>1819281</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1877080</t>
+          <t>1879382</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1739690</t>
+          <t>1739594</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1799871</t>
+          <t>1799431</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3580011</t>
+          <t>3580057</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3661922</t>
+          <t>3666316</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,2%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42779</t>
+          <t>42536</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72631</t>
+          <t>72504</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20974</t>
+          <t>20142</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45575</t>
+          <t>47229</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69871</t>
+          <t>70448</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>110774</t>
+          <t>110277</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>474255</t>
+          <t>474382</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>504107</t>
+          <t>504350</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>503565</t>
+          <t>501911</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>528166</t>
+          <t>528998</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>985253</t>
+          <t>985750</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1026156</t>
+          <t>1025579</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,57%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>474778</t>
+          <t>469529</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>562110</t>
+          <t>555415</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>578552</t>
+          <t>581449</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>676329</t>
+          <t>679234</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1076526</t>
+          <t>1076896</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1200325</t>
+          <t>1206419</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,46%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2815508</t>
+          <t>2822203</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2902840</t>
+          <t>2908089</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2855771</t>
+          <t>2852866</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2953548</t>
+          <t>2950651</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5709393</t>
+          <t>5703299</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5833192</t>
+          <t>5832822</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,41%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>185268</t>
+          <t>202054</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>166119</t>
+          <t>181934</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>204251</t>
+          <t>225147</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>375862</t>
+          <t>399259</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>353369</t>
+          <t>377121</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>395832</t>
+          <t>421573</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>561130</t>
+          <t>601313</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>531866</t>
+          <t>569246</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>591756</t>
+          <t>630171</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>45,1%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>328125</t>
+          <t>374928</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>309142</t>
+          <t>351835</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>347274</t>
+          <t>395048</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>376185</t>
+          <t>420881</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>356215</t>
+          <t>398567</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>398678</t>
+          <t>443019</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>704310</t>
+          <t>795809</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>673684</t>
+          <t>766951</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>733574</t>
+          <t>827876</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>59,26%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>513393</t>
+          <t>576982</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513393</t>
+          <t>576982</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>513393</t>
+          <t>576982</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>752047</t>
+          <t>820140</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>752047</t>
+          <t>820140</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>752047</t>
+          <t>820140</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1265440</t>
+          <t>1397122</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1265440</t>
+          <t>1397122</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1265440</t>
+          <t>1397122</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>324373</t>
+          <t>349775</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>233827</t>
+          <t>317733</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>377269</t>
+          <t>381978</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>469185</t>
+          <t>295123</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>279689</t>
+          <t>270242</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>928864</t>
+          <t>321280</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>793558</t>
+          <t>644898</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>587517</t>
+          <t>601746</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1407601</t>
+          <t>687348</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1964427</t>
+          <t>1878919</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1911531</t>
+          <t>1846716</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2054973</t>
+          <t>1910961</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1765681</t>
+          <t>1873249</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1306002</t>
+          <t>1847092</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1955177</t>
+          <t>1898130</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3730108</t>
+          <t>3752168</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3116065</t>
+          <t>3709718</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3936149</t>
+          <t>3795320</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,31%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2288800</t>
+          <t>2228694</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2288800</t>
+          <t>2228694</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2288800</t>
+          <t>2228694</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2234866</t>
+          <t>2168372</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2234866</t>
+          <t>2168372</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2234866</t>
+          <t>2168372</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4523666</t>
+          <t>4397066</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4523666</t>
+          <t>4397066</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4523666</t>
+          <t>4397066</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>110875</t>
+          <t>121996</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94027</t>
+          <t>104688</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>130073</t>
+          <t>143357</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>73746</t>
+          <t>85395</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63230</t>
+          <t>72231</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87847</t>
+          <t>102107</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>184620</t>
+          <t>207391</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>162333</t>
+          <t>185856</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>204839</t>
+          <t>232785</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>534569</t>
+          <t>587246</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>515371</t>
+          <t>565885</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>551417</t>
+          <t>604554</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>586557</t>
+          <t>648800</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>572456</t>
+          <t>632088</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>597073</t>
+          <t>661964</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1121127</t>
+          <t>1236045</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1100908</t>
+          <t>1210651</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1143414</t>
+          <t>1257580</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,12%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>645444</t>
+          <t>709242</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>645444</t>
+          <t>709242</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>645444</t>
+          <t>709242</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660303</t>
+          <t>734195</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660303</t>
+          <t>734195</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660303</t>
+          <t>734195</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1305747</t>
+          <t>1443436</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1305747</t>
+          <t>1443436</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1305747</t>
+          <t>1443436</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>620516</t>
+          <t>673824</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>483570</t>
+          <t>623092</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>684182</t>
+          <t>715848</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>918793</t>
+          <t>779777</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>739539</t>
+          <t>737624</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1473218</t>
+          <t>818769</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1539309</t>
+          <t>1453602</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1311747</t>
+          <t>1396797</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2095643</t>
+          <t>1515663</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>20,94%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2827121</t>
+          <t>2841093</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2763455</t>
+          <t>2799069</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2964067</t>
+          <t>2891825</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2728423</t>
+          <t>2942930</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2173998</t>
+          <t>2903938</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2907677</t>
+          <t>2985083</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5555544</t>
+          <t>5784023</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4999210</t>
+          <t>5721962</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5783106</t>
+          <t>5840828</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>80,7%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3447637</t>
+          <t>3514917</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3447637</t>
+          <t>3514917</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3447637</t>
+          <t>3514917</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3647216</t>
+          <t>3722707</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3647216</t>
+          <t>3722707</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3647216</t>
+          <t>3722707</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7094853</t>
+          <t>7237625</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7094853</t>
+          <t>7237625</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7094853</t>
+          <t>7237625</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
